--- a/employee_surveys/046_team_member_of_the_month_vote--employee_surveys.xlsx
+++ b/employee_surveys/046_team_member_of_the_month_vote--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>team_member_of_the_month_2</t>
+          <t>team_member_of_the_month_2_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Why Vote For This Team Member?</t>
+          <t>Team Member Of The Month 2 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>When Did You First Notice This Team Member's Outstanding Contribution?</t>
+          <t>Team Member Of The Month 6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Time Spent With This Team Member?</t>
+          <t>Team Member Of The Month 8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How Often Do You Interact With This Team Member?</t>
+          <t>Team Member Of The Month 12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Team Member Of The Month Vote</t>
+          <t>Team Member Of The Month 15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'john',_'value':_1}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'John', 'value': 1}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'jane',_'value':_2}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Jane', 'value': 2}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'jack',_'value':_3}</t>
+          <t>jack</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Jack', 'value': 3}</t>
+          <t>Jack</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'john',_'value':_1}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'John', 'value': 1}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'jane',_'value':_2}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Jane', 'value': 2}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'jack',_'value':_3}</t>
+          <t>jack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Jack', 'value': 3}</t>
+          <t>Jack</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'daily',_'value':_1}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Daily', 'value': 1}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'several_times_a_week',_'value':_2}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Several times a week', 'value': 2}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'once_a_week',_'value':_4}</t>
+          <t>once_a_week</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Once a week', 'value': 4}</t>
+          <t>Once a week</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'daily',_'value':_1}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Daily', 'value': 1}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'several_times_a_week',_'value':_2}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Several times a week', 'value': 2}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'once_a_week',_'value':_4}</t>
+          <t>once_a_week</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Once a week', 'value': 4}</t>
+          <t>Once a week</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'team_member_1',_'value':_1}</t>
+          <t>team_member_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Team Member 1', 'value': 1}</t>
+          <t>Team Member 1</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'team_member_2',_'value':_2}</t>
+          <t>team_member_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Team Member 2', 'value': 2}</t>
+          <t>Team Member 2</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'team_member_3',_'value':_3}</t>
+          <t>team_member_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Team Member 3', 'value': 3}</t>
+          <t>Team Member 3</t>
         </is>
       </c>
     </row>
